--- a/JsonConverter/ExcelFiles/OO_Stage2CueSheet.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage2CueSheet.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +32,16 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -95,6 +108,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1303,7 +1328,7 @@
       </c>
     </row>
     <row r="4" ht="58" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Stage2_CueSheet_01</t>
         </is>
@@ -1383,9 +1408,9 @@
           <t>Stage2_Road_Quest_01</t>
         </is>
       </c>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>?? ??? ? ????? ??? ?????.</t>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>서쪽 도시에 가 탐관오리의 자택을 방문하세요.</t>
         </is>
       </c>
       <c r="R4" s="4" t="inlineStr">
@@ -1433,22 +1458,22 @@
           <t>OO_KimchiStew_1</t>
         </is>
       </c>
-      <c r="AA4" s="4" t="inlineStr">
+      <c r="AA4" s="7" t="inlineStr">
         <is>
           <t>Ing_Honey_01</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="n">
+      <c r="AB4" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ing_Honey_01|OO_KoreanCake_1|Ing_Rice_01</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>10|10|10</t>
+      <c r="AC4" s="8" t="inlineStr">
+        <is>
+          <t>Ing_Rice_01|Ing_Honey_01</t>
+        </is>
+      </c>
+      <c r="AD4" s="8" t="inlineStr">
+        <is>
+          <t>10|10</t>
         </is>
       </c>
       <c r="AE4" s="4" t="inlineStr">
@@ -1490,9 +1515,9 @@
       <c r="AO4" s="4" t="n">
         <v>230</v>
       </c>
-      <c r="AP4" s="4" t="inlineStr">
-        <is>
-          <t>?</t>
+      <c r="AP4" s="7" t="inlineStr">
+        <is>
+          <t>!</t>
         </is>
       </c>
       <c r="AQ4" s="4" t="inlineStr">

--- a/JsonConverter/ExcelFiles/OO_Stage2CueSheet.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Stage2CueSheet.xlsx
@@ -1495,7 +1495,7 @@
         <v>145</v>
       </c>
       <c r="AI4" s="4" t="n">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="AJ4" s="4" t="n">
         <v>4</v>
